--- a/outputs/E_eighteen_columns.xlsx
+++ b/outputs/E_eighteen_columns.xlsx
@@ -10,25 +10,27 @@
     <sheet name="Data 1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Validation Report" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Page Audit" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Provenance" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Read me" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Cell Evidence" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Verification" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Constraints" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Repair Proposals" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Correction History" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Join Receipt" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Provenance" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Read me" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cell Evidence" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Verification" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Constraints" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Repair Proposals" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Correction History" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data 1'!$A$1:$R$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Validation Report'!$A$1:$H$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Page Audit'!$A$1:$L$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Provenance'!$A$1:$E$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Read me'!$A$1:$B$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Cell Evidence'!$A$1:$M$181</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Verification'!$A$1:$B$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Constraints'!$A$1:$H$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Repair Proposals'!$A$1:$I$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Correction History'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Join Receipt'!$A$1:$H$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Provenance'!$A$1:$E$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Read me'!$A$1:$B$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Cell Evidence'!$A$1:$O$181</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Verification'!$A$1:$B$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Constraints'!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Repair Proposals'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Correction History'!$A$1:$I$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -36,7 +38,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -86,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -98,6 +102,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1304,6 +1311,79 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Excel row</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Observed</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Supporting equations</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Caution</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
@@ -1563,7 +1643,7 @@
         <v>0.92</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.052</v>
+        <v>0.043</v>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
@@ -1605,7 +1685,7 @@
         <v>0.92</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>1.186</v>
+        <v>0.571</v>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
@@ -1647,7 +1727,7 @@
         <v>0.92</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.946</v>
+        <v>0.718</v>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
@@ -1678,6 +1758,103 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Data sheet</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Source pages</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Page joins</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Repeated headers removed</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Split rows recovered</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>PDF page</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Source rows on page</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Output rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="17" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1915,7 +2092,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1959,7 +2136,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>3.689</v>
+        <v>7.369</v>
       </c>
     </row>
     <row r="4" ht="119" customHeight="1">
@@ -2088,13 +2265,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M181"/>
+  <dimension ref="A1:O181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2110,6 +2287,8 @@
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="17" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="65" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -2178,6 +2357,16 @@
           <t>Role</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Location status</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Location reason</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="17" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
@@ -2223,6 +2412,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N2" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O2" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="17" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
@@ -2268,6 +2467,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
@@ -2313,6 +2522,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -2358,6 +2577,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -2403,6 +2632,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O6" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -2448,6 +2687,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -2493,6 +2742,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O8" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
@@ -2538,6 +2797,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
@@ -2583,6 +2852,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O10" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
@@ -2628,6 +2907,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O11" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
@@ -2673,6 +2962,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O12" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
@@ -2718,6 +3017,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O13" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
@@ -2763,6 +3072,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O14" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
@@ -2808,6 +3127,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O15" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
@@ -2853,6 +3182,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N16" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O16" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="17" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
@@ -2898,6 +3237,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O17" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="17" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
@@ -2943,6 +3292,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N18" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O18" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="17" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
@@ -2988,6 +3347,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O19" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="17" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
@@ -3033,6 +3402,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O20" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="17" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
@@ -3078,6 +3457,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O21" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="17" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
@@ -3123,6 +3512,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N22" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O22" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="17" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
@@ -3168,6 +3567,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N23" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O23" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="17" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
@@ -3213,6 +3622,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N24" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O24" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="17" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
@@ -3258,6 +3677,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N25" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O25" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="17" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
@@ -3303,6 +3732,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N26" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O26" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="17" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
@@ -3348,6 +3787,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N27" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O27" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="17" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
@@ -3393,6 +3842,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N28" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O28" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="17" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
@@ -3438,6 +3897,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N29" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O29" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="17" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
@@ -3483,6 +3952,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N30" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O30" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="17" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
@@ -3528,6 +4007,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N31" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O31" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="17" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
@@ -3573,6 +4062,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N32" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O32" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="17" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
@@ -3618,6 +4117,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N33" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O33" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="17" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
@@ -3663,6 +4172,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N34" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O34" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="17" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
@@ -3708,6 +4227,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N35" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O35" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="17" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
@@ -3753,6 +4282,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N36" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O36" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="17" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
@@ -3798,6 +4337,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N37" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O37" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="17" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
@@ -3843,6 +4392,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N38" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O38" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="17" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
@@ -3888,6 +4447,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N39" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O39" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="17" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
@@ -3933,6 +4502,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N40" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O40" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="17" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
@@ -3978,6 +4557,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N41" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O41" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="17" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
@@ -4023,6 +4612,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N42" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O42" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="17" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
@@ -4068,6 +4667,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N43" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O43" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="17" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
@@ -4113,6 +4722,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N44" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O44" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="17" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
@@ -4158,6 +4777,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N45" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O45" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="17" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
@@ -4203,6 +4832,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N46" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O46" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="17" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
@@ -4248,6 +4887,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N47" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O47" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="17" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
@@ -4293,6 +4942,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N48" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O48" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="17" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
@@ -4338,6 +4997,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N49" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O49" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="17" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
@@ -4383,6 +5052,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N50" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O50" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="17" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
@@ -4428,6 +5107,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N51" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O51" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="17" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
@@ -4473,6 +5162,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N52" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O52" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="17" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
@@ -4518,6 +5217,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N53" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O53" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="17" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
@@ -4563,6 +5272,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N54" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O54" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="17" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
@@ -4608,6 +5327,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N55" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O55" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="17" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
@@ -4653,6 +5382,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N56" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O56" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="17" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
@@ -4698,6 +5437,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N57" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O57" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="17" customHeight="1">
       <c r="A58" s="4" t="inlineStr">
@@ -4743,6 +5492,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N58" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O58" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="17" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
@@ -4788,6 +5547,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N59" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O59" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="17" customHeight="1">
       <c r="A60" s="4" t="inlineStr">
@@ -4833,6 +5602,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N60" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O60" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="17" customHeight="1">
       <c r="A61" s="4" t="inlineStr">
@@ -4878,6 +5657,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N61" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O61" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="17" customHeight="1">
       <c r="A62" s="4" t="inlineStr">
@@ -4923,6 +5712,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N62" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O62" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="17" customHeight="1">
       <c r="A63" s="4" t="inlineStr">
@@ -4968,6 +5767,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N63" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O63" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="17" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
@@ -5013,6 +5822,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N64" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O64" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="17" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
@@ -5058,6 +5877,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N65" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O65" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="17" customHeight="1">
       <c r="A66" s="4" t="inlineStr">
@@ -5103,6 +5932,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N66" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O66" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="17" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
@@ -5148,6 +5987,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N67" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O67" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="17" customHeight="1">
       <c r="A68" s="4" t="inlineStr">
@@ -5193,6 +6042,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N68" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O68" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="17" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
@@ -5238,6 +6097,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N69" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O69" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="17" customHeight="1">
       <c r="A70" s="4" t="inlineStr">
@@ -5283,6 +6152,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N70" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O70" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="17" customHeight="1">
       <c r="A71" s="4" t="inlineStr">
@@ -5328,6 +6207,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N71" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O71" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="17" customHeight="1">
       <c r="A72" s="4" t="inlineStr">
@@ -5373,6 +6262,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N72" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O72" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="17" customHeight="1">
       <c r="A73" s="4" t="inlineStr">
@@ -5418,6 +6317,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N73" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O73" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="17" customHeight="1">
       <c r="A74" s="4" t="inlineStr">
@@ -5463,6 +6372,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N74" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O74" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="17" customHeight="1">
       <c r="A75" s="4" t="inlineStr">
@@ -5508,6 +6427,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N75" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O75" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="17" customHeight="1">
       <c r="A76" s="4" t="inlineStr">
@@ -5553,6 +6482,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N76" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O76" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="17" customHeight="1">
       <c r="A77" s="4" t="inlineStr">
@@ -5598,6 +6537,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N77" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O77" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="17" customHeight="1">
       <c r="A78" s="4" t="inlineStr">
@@ -5643,6 +6592,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N78" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O78" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="17" customHeight="1">
       <c r="A79" s="4" t="inlineStr">
@@ -5688,6 +6647,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N79" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O79" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="17" customHeight="1">
       <c r="A80" s="4" t="inlineStr">
@@ -5733,6 +6702,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N80" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O80" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="17" customHeight="1">
       <c r="A81" s="4" t="inlineStr">
@@ -5778,6 +6757,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N81" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O81" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="17" customHeight="1">
       <c r="A82" s="4" t="inlineStr">
@@ -5823,6 +6812,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N82" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O82" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="17" customHeight="1">
       <c r="A83" s="4" t="inlineStr">
@@ -5868,6 +6867,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N83" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O83" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="17" customHeight="1">
       <c r="A84" s="4" t="inlineStr">
@@ -5913,6 +6922,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N84" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O84" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="17" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
@@ -5958,6 +6977,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N85" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O85" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="17" customHeight="1">
       <c r="A86" s="4" t="inlineStr">
@@ -6003,6 +7032,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N86" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O86" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="17" customHeight="1">
       <c r="A87" s="4" t="inlineStr">
@@ -6048,6 +7087,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N87" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O87" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="17" customHeight="1">
       <c r="A88" s="4" t="inlineStr">
@@ -6093,6 +7142,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N88" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O88" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="17" customHeight="1">
       <c r="A89" s="4" t="inlineStr">
@@ -6138,6 +7197,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N89" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O89" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="17" customHeight="1">
       <c r="A90" s="4" t="inlineStr">
@@ -6183,6 +7252,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N90" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O90" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="17" customHeight="1">
       <c r="A91" s="4" t="inlineStr">
@@ -6228,6 +7307,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N91" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O91" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="17" customHeight="1">
       <c r="A92" s="4" t="inlineStr">
@@ -6273,6 +7362,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N92" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O92" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="17" customHeight="1">
       <c r="A93" s="4" t="inlineStr">
@@ -6318,6 +7417,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N93" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O93" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="17" customHeight="1">
       <c r="A94" s="4" t="inlineStr">
@@ -6363,6 +7472,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N94" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O94" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="17" customHeight="1">
       <c r="A95" s="4" t="inlineStr">
@@ -6408,6 +7527,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N95" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O95" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="17" customHeight="1">
       <c r="A96" s="4" t="inlineStr">
@@ -6453,6 +7582,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N96" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O96" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="17" customHeight="1">
       <c r="A97" s="4" t="inlineStr">
@@ -6498,6 +7637,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N97" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O97" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="17" customHeight="1">
       <c r="A98" s="4" t="inlineStr">
@@ -6543,6 +7692,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N98" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O98" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="17" customHeight="1">
       <c r="A99" s="4" t="inlineStr">
@@ -6588,6 +7747,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N99" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O99" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="17" customHeight="1">
       <c r="A100" s="4" t="inlineStr">
@@ -6633,6 +7802,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N100" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O100" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="17" customHeight="1">
       <c r="A101" s="4" t="inlineStr">
@@ -6678,6 +7857,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N101" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O101" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="17" customHeight="1">
       <c r="A102" s="4" t="inlineStr">
@@ -6723,6 +7912,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N102" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O102" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="17" customHeight="1">
       <c r="A103" s="4" t="inlineStr">
@@ -6768,6 +7967,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N103" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O103" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="17" customHeight="1">
       <c r="A104" s="4" t="inlineStr">
@@ -6813,6 +8022,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N104" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O104" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="17" customHeight="1">
       <c r="A105" s="4" t="inlineStr">
@@ -6858,6 +8077,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N105" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O105" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="17" customHeight="1">
       <c r="A106" s="4" t="inlineStr">
@@ -6903,6 +8132,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N106" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O106" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="17" customHeight="1">
       <c r="A107" s="4" t="inlineStr">
@@ -6948,6 +8187,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N107" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O107" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="17" customHeight="1">
       <c r="A108" s="4" t="inlineStr">
@@ -6993,6 +8242,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N108" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O108" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="17" customHeight="1">
       <c r="A109" s="4" t="inlineStr">
@@ -7038,6 +8297,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N109" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O109" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="17" customHeight="1">
       <c r="A110" s="4" t="inlineStr">
@@ -7083,6 +8352,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N110" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O110" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="17" customHeight="1">
       <c r="A111" s="4" t="inlineStr">
@@ -7128,6 +8407,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N111" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O111" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="17" customHeight="1">
       <c r="A112" s="4" t="inlineStr">
@@ -7173,6 +8462,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N112" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O112" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="17" customHeight="1">
       <c r="A113" s="4" t="inlineStr">
@@ -7218,6 +8517,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N113" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O113" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="17" customHeight="1">
       <c r="A114" s="4" t="inlineStr">
@@ -7263,6 +8572,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N114" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O114" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="17" customHeight="1">
       <c r="A115" s="4" t="inlineStr">
@@ -7308,6 +8627,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N115" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O115" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="17" customHeight="1">
       <c r="A116" s="4" t="inlineStr">
@@ -7353,6 +8682,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N116" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O116" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="17" customHeight="1">
       <c r="A117" s="4" t="inlineStr">
@@ -7398,6 +8737,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N117" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O117" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="17" customHeight="1">
       <c r="A118" s="4" t="inlineStr">
@@ -7443,6 +8792,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N118" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O118" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="17" customHeight="1">
       <c r="A119" s="4" t="inlineStr">
@@ -7488,6 +8847,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N119" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O119" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="17" customHeight="1">
       <c r="A120" s="4" t="inlineStr">
@@ -7533,6 +8902,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N120" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O120" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="17" customHeight="1">
       <c r="A121" s="4" t="inlineStr">
@@ -7578,6 +8957,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N121" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O121" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="17" customHeight="1">
       <c r="A122" s="4" t="inlineStr">
@@ -7623,6 +9012,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N122" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O122" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="17" customHeight="1">
       <c r="A123" s="4" t="inlineStr">
@@ -7668,6 +9067,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N123" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O123" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="17" customHeight="1">
       <c r="A124" s="4" t="inlineStr">
@@ -7713,6 +9122,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N124" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O124" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="17" customHeight="1">
       <c r="A125" s="4" t="inlineStr">
@@ -7758,6 +9177,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N125" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O125" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="17" customHeight="1">
       <c r="A126" s="4" t="inlineStr">
@@ -7803,6 +9232,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N126" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O126" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="17" customHeight="1">
       <c r="A127" s="4" t="inlineStr">
@@ -7848,6 +9287,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N127" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O127" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="17" customHeight="1">
       <c r="A128" s="4" t="inlineStr">
@@ -7893,6 +9342,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N128" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O128" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="17" customHeight="1">
       <c r="A129" s="4" t="inlineStr">
@@ -7938,6 +9397,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N129" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O129" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="17" customHeight="1">
       <c r="A130" s="4" t="inlineStr">
@@ -7983,6 +9452,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N130" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O130" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="17" customHeight="1">
       <c r="A131" s="4" t="inlineStr">
@@ -8028,6 +9507,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N131" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O131" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="17" customHeight="1">
       <c r="A132" s="4" t="inlineStr">
@@ -8073,6 +9562,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N132" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O132" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="17" customHeight="1">
       <c r="A133" s="4" t="inlineStr">
@@ -8118,6 +9617,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N133" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O133" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="17" customHeight="1">
       <c r="A134" s="4" t="inlineStr">
@@ -8163,6 +9672,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N134" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O134" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="135" ht="17" customHeight="1">
       <c r="A135" s="4" t="inlineStr">
@@ -8208,6 +9727,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N135" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O135" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="17" customHeight="1">
       <c r="A136" s="4" t="inlineStr">
@@ -8253,6 +9782,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N136" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O136" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="17" customHeight="1">
       <c r="A137" s="4" t="inlineStr">
@@ -8298,6 +9837,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N137" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O137" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="17" customHeight="1">
       <c r="A138" s="4" t="inlineStr">
@@ -8343,6 +9892,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N138" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O138" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="139" ht="17" customHeight="1">
       <c r="A139" s="4" t="inlineStr">
@@ -8388,6 +9947,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N139" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O139" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="140" ht="17" customHeight="1">
       <c r="A140" s="4" t="inlineStr">
@@ -8433,6 +10002,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N140" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O140" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="141" ht="17" customHeight="1">
       <c r="A141" s="4" t="inlineStr">
@@ -8478,6 +10057,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N141" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O141" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="142" ht="17" customHeight="1">
       <c r="A142" s="4" t="inlineStr">
@@ -8523,6 +10112,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N142" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O142" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="143" ht="17" customHeight="1">
       <c r="A143" s="4" t="inlineStr">
@@ -8568,6 +10167,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N143" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O143" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="144" ht="17" customHeight="1">
       <c r="A144" s="4" t="inlineStr">
@@ -8613,6 +10222,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N144" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O144" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="145" ht="17" customHeight="1">
       <c r="A145" s="4" t="inlineStr">
@@ -8658,6 +10277,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N145" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O145" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="146" ht="17" customHeight="1">
       <c r="A146" s="4" t="inlineStr">
@@ -8703,6 +10332,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N146" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O146" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="147" ht="17" customHeight="1">
       <c r="A147" s="4" t="inlineStr">
@@ -8748,6 +10387,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N147" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O147" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="148" ht="17" customHeight="1">
       <c r="A148" s="4" t="inlineStr">
@@ -8793,6 +10442,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N148" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O148" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="149" ht="17" customHeight="1">
       <c r="A149" s="4" t="inlineStr">
@@ -8838,6 +10497,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N149" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O149" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="150" ht="17" customHeight="1">
       <c r="A150" s="4" t="inlineStr">
@@ -8883,6 +10552,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N150" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O150" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="151" ht="17" customHeight="1">
       <c r="A151" s="4" t="inlineStr">
@@ -8928,6 +10607,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N151" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O151" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="152" ht="17" customHeight="1">
       <c r="A152" s="4" t="inlineStr">
@@ -8973,6 +10662,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N152" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O152" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="153" ht="17" customHeight="1">
       <c r="A153" s="4" t="inlineStr">
@@ -9018,6 +10717,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N153" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O153" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="154" ht="17" customHeight="1">
       <c r="A154" s="4" t="inlineStr">
@@ -9063,6 +10772,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N154" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O154" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="155" ht="17" customHeight="1">
       <c r="A155" s="4" t="inlineStr">
@@ -9108,6 +10827,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N155" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O155" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="156" ht="17" customHeight="1">
       <c r="A156" s="4" t="inlineStr">
@@ -9153,6 +10882,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N156" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O156" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="157" ht="17" customHeight="1">
       <c r="A157" s="4" t="inlineStr">
@@ -9198,6 +10937,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N157" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O157" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="158" ht="17" customHeight="1">
       <c r="A158" s="4" t="inlineStr">
@@ -9243,6 +10992,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N158" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O158" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="159" ht="17" customHeight="1">
       <c r="A159" s="4" t="inlineStr">
@@ -9288,6 +11047,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N159" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O159" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="160" ht="17" customHeight="1">
       <c r="A160" s="4" t="inlineStr">
@@ -9333,6 +11102,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N160" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O160" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="161" ht="17" customHeight="1">
       <c r="A161" s="4" t="inlineStr">
@@ -9378,6 +11157,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N161" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O161" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="162" ht="17" customHeight="1">
       <c r="A162" s="4" t="inlineStr">
@@ -9423,6 +11212,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N162" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O162" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="163" ht="17" customHeight="1">
       <c r="A163" s="4" t="inlineStr">
@@ -9468,6 +11267,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N163" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O163" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="164" ht="17" customHeight="1">
       <c r="A164" s="4" t="inlineStr">
@@ -9513,6 +11322,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N164" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O164" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="165" ht="17" customHeight="1">
       <c r="A165" s="4" t="inlineStr">
@@ -9558,6 +11377,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N165" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O165" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="166" ht="17" customHeight="1">
       <c r="A166" s="4" t="inlineStr">
@@ -9603,6 +11432,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N166" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O166" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="167" ht="17" customHeight="1">
       <c r="A167" s="4" t="inlineStr">
@@ -9648,6 +11487,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N167" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O167" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="168" ht="17" customHeight="1">
       <c r="A168" s="4" t="inlineStr">
@@ -9693,6 +11542,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N168" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O168" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="169" ht="17" customHeight="1">
       <c r="A169" s="4" t="inlineStr">
@@ -9738,6 +11597,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N169" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O169" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="170" ht="17" customHeight="1">
       <c r="A170" s="4" t="inlineStr">
@@ -9783,6 +11652,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N170" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O170" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="171" ht="17" customHeight="1">
       <c r="A171" s="4" t="inlineStr">
@@ -9828,6 +11707,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N171" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O171" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="172" ht="17" customHeight="1">
       <c r="A172" s="4" t="inlineStr">
@@ -9873,6 +11762,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N172" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O172" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="173" ht="17" customHeight="1">
       <c r="A173" s="4" t="inlineStr">
@@ -9918,6 +11817,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N173" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O173" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="174" ht="17" customHeight="1">
       <c r="A174" s="4" t="inlineStr">
@@ -9963,6 +11872,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N174" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O174" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="175" ht="17" customHeight="1">
       <c r="A175" s="4" t="inlineStr">
@@ -10008,6 +11927,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N175" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O175" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="176" ht="17" customHeight="1">
       <c r="A176" s="4" t="inlineStr">
@@ -10053,6 +11982,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N176" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O176" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="177" ht="17" customHeight="1">
       <c r="A177" s="4" t="inlineStr">
@@ -10098,6 +12037,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N177" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O177" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="178" ht="17" customHeight="1">
       <c r="A178" s="4" t="inlineStr">
@@ -10143,6 +12092,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N178" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O178" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="179" ht="17" customHeight="1">
       <c r="A179" s="4" t="inlineStr">
@@ -10188,6 +12147,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N179" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O179" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="180" ht="17" customHeight="1">
       <c r="A180" s="4" t="inlineStr">
@@ -10233,6 +12202,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N180" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O180" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="181" ht="17" customHeight="1">
       <c r="A181" s="4" t="inlineStr">
@@ -10278,23 +12257,33 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N181" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O181" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M181"/>
+  <autoFilter ref="A1:O181"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="43" customWidth="1" min="1" max="1"/>
     <col width="65" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -10330,7 +12319,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>7cb98b1e9d9e04bbb16b1ed3517aee41df67eaf747f35ff89b3008801904c4f7</t>
+          <t>5fec702c69e139be23884b9902cadf2b52978fdc3c5904e7ff2b4cf706f89875</t>
         </is>
       </c>
     </row>
@@ -10369,37 +12358,39 @@
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>cells</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>162</v>
+          <t>Export type</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Draft Excel</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>cells with source boxes</t>
+          <t>Non-empty exported cells</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>162</v>
+        <v>180</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>equations</t>
+          <t>Cells with source boxes</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>equation checks</t>
+          <t>Cells requiring full-page evidence review</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
@@ -10409,30 +12400,80 @@
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>failed equation checks</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>0</v>
+          <t>Cell source-box coverage</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
+          <t>cells</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="13" ht="17" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>cells with source boxes</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>equations</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>equation checks</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="17" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>failed equation checks</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="17" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
           <t>proposals with multiple equations</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B17" s="4" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B12"/>
+  <autoFilter ref="A1:B17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10497,77 +12538,4 @@
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Excel row</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Column</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Supporting equations</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Evidence</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>State</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Caution</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:I1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>